--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/araucania.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/araucania.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1379.43</v>
+        <v>1372.35</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>5314.76</v>
+        <v>5287.45</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1572.11</v>
+        <v>1556.42</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>7329.43</v>
+        <v>7289.36</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>962.71</v>
+        <v>973.1799999999999</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>769.65</v>
+        <v>782.9299999999999</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>2779.09</v>
+        <v>2827.06</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>4420.12</v>
+        <v>4450.75</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>885.12</v>
+        <v>891.25</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>890.24</v>
+        <v>896.41</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>880.22</v>
+        <v>886.3200000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>3593.29</v>
+        <v>3610.02</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>2932.09</v>
+        <v>2926.89</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1028.11</v>
+        <v>1023.87</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>1698.22</v>
+        <v>1695.59</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>8945.790000000001</v>
+        <v>8991.99</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>29977.64</v>
+        <v>30132.45</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>7431.46</v>
+        <v>7469.84</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>2140.32</v>
+        <v>2112.66</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1122.56</v>
+        <v>1108.05</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>59369.11</v>
+        <v>58778.41</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1069.81</v>
+        <v>1059.17</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>760.58</v>
+        <v>753.01</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>7361.87</v>
+        <v>7288.62</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>4994.77</v>
+        <v>4976.86</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>7853.03</v>
+        <v>7824.87</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>3457.75</v>
+        <v>3443.26</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>789.7</v>
+        <v>786.39</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>7607.82</v>
+        <v>7575.92</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>33828.92</v>
+        <v>33687.1</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>24542.47</v>
+        <v>24334.57</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>5965.18</v>
+        <v>5960.38</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>72933.34</v>
+        <v>72874.72</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>2263.54</v>
+        <v>2261.72</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>21582.97</v>
+        <v>21665.81</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>2943.3</v>
+        <v>2939.17</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>8169.49</v>
+        <v>8158.03</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>1351.84</v>
+        <v>1349.94</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>3895.88</v>
+        <v>3900.88</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>30098.27</v>
+        <v>30305.44</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>964.4299999999999</v>
+        <v>971.0700000000001</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>7831.95</v>
+        <v>7885.85</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>1135.34</v>
+        <v>1147.52</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>3601.98</v>
+        <v>3646.25</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>1173.94</v>
+        <v>1180.36</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>2387.11</v>
+        <v>2400.16</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>1827.47</v>
+        <v>1801.28</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>3219.05</v>
+        <v>3172.91</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>1846.99</v>
+        <v>1820.52</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>6035.71</v>
+        <v>5949.2</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>12103.74</v>
+        <v>11930.25</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>12103.74</v>
+        <v>11930.25</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>2017.29</v>
+        <v>1988.38</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>3044.34</v>
+        <v>3048.56</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>42407.99</v>
+        <v>42685.93</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>56563.14</v>
+        <v>56933.85</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>3161.97</v>
+        <v>3210.11</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>2595.49</v>
+        <v>2635</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>56966.32</v>
+        <v>57833.58</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>2749.63</v>
+        <v>2791.49</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>1157.74</v>
+        <v>1175.36</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>1852.38</v>
+        <v>1880.58</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>17076.62</v>
+        <v>17336.6</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>868.3</v>
+        <v>881.52</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>983.97</v>
+        <v>1007.9</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>5041.96</v>
+        <v>5169.42</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>1176.16</v>
+        <v>1205.89</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>1898.05</v>
+        <v>1955.6</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>7580.15</v>
+        <v>7805.45</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>1185.16</v>
+        <v>1220.38</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>1810.01</v>
+        <v>1815.26</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>2927.82</v>
+        <v>2936.3</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>942.46</v>
+        <v>938.48</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>1518.02</v>
+        <v>1511.62</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>1895.97</v>
+        <v>1901.18</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>18657.17</v>
+        <v>18826.87</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>1381.84</v>
+        <v>1394.41</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>5160.18</v>
+        <v>5207.12</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>969.92</v>
+        <v>978.74</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>862.33</v>
+        <v>870.17</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>3708.89</v>
+        <v>3742.63</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>823.13</v>
+        <v>830.61</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>4780.34</v>
+        <v>4813.62</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>8303.549999999999</v>
+        <v>8361.360000000001</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>817.59</v>
+        <v>822.97</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>3090.59</v>
+        <v>3110.94</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>31152.43</v>
+        <v>31357.59</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>57411.89</v>
+        <v>57923.24</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>1631.17</v>
+        <v>1645.7</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>18756.87</v>
+        <v>18923.94</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>1994.18</v>
+        <v>1990.77</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>1739.4</v>
+        <v>1726.94</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>1206.22</v>
+        <v>1204.45</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>825.15</v>
+        <v>820.14</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>846.33</v>
+        <v>843.0700000000001</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>7464.46</v>
+        <v>7503.11</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>2429.51</v>
+        <v>2431.85</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>11599.54</v>
+        <v>11610.72</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>11066.47</v>
+        <v>11077.14</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>1102.45</v>
+        <v>1151.13</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>2313.26</v>
+        <v>2380.45</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>10991.77</v>
+        <v>11035.11</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>3135.69</v>
+        <v>3095.32</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>6288.12</v>
+        <v>6386.62</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>24678.79</v>
+        <v>24677.52</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>891.63</v>
+        <v>891.58</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>7027.68</v>
+        <v>6996.26</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>10359.5</v>
+        <v>10313.18</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>9042.549999999999</v>
+        <v>9050.34</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>7223.85</v>
+        <v>7230.07</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>8078.32</v>
+        <v>8085.28</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>783.92</v>
+        <v>784.6</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>2007.91</v>
+        <v>2016.2</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>1254.28</v>
+        <v>1259.46</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>1107.17</v>
+        <v>1111.74</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>783.92</v>
+        <v>787.16</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>810.6</v>
+        <v>813.95</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>7037.26</v>
+        <v>7017.85</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>2637.72</v>
+        <v>2630.45</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>5415.65</v>
+        <v>5353.13</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>6271.38</v>
+        <v>6177.84</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>25678.57</v>
+        <v>25531.07</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>2745.61</v>
+        <v>2728.02</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>1294.34</v>
+        <v>1288.76</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>1934.34</v>
+        <v>1926.01</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>2237.46</v>
+        <v>2227.82</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>1490.23</v>
+        <v>1468.67</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>20803.64</v>
+        <v>20502.67</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>12621.64</v>
+        <v>12439.04</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>4665.95</v>
+        <v>4565.56</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>1539.28</v>
+        <v>1506.16</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>3282.94</v>
+        <v>3206.55</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>1834.65</v>
+        <v>1791.96</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>1948.27</v>
+        <v>1886.15</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>13108.86</v>
+        <v>12850.34</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>1894.02</v>
+        <v>1856.66</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>1424.41</v>
+        <v>1396.32</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>5682.59</v>
+        <v>5570.53</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>918.52</v>
+        <v>894.33</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>9731.84</v>
+        <v>9475.57</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>4172.2</v>
+        <v>4096.53</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>1781.88</v>
+        <v>1749.56</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>1086.51</v>
+        <v>1057.42</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>5821.1</v>
+        <v>5665.23</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>12137.54</v>
+        <v>12187.98</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>1597.19</v>
+        <v>1603.83</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>1691.79</v>
+        <v>1698.82</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>5831.96</v>
+        <v>5856.19</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>11656.44</v>
+        <v>11755.37</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>2300.99</v>
+        <v>2297.14</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>797.67</v>
+        <v>807.49</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>1002.7</v>
+        <v>1015.04</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>1783.65</v>
+        <v>1805.6</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>7782.37</v>
+        <v>7878.15</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>3444.43</v>
+        <v>3490.28</v>
       </c>
     </row>
     <row r="157">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>2035.71</v>
+        <v>2062.82</v>
       </c>
     </row>
     <row r="158">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>2798.47</v>
+        <v>2834.99</v>
       </c>
     </row>
     <row r="159">
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>2215.46</v>
+        <v>2269.98</v>
       </c>
     </row>
     <row r="160">
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>12219.99</v>
+        <v>12520.73</v>
       </c>
     </row>
     <row r="161">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>4183.17</v>
+        <v>4262.28</v>
       </c>
     </row>
     <row r="162">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>2799.11</v>
+        <v>2852.05</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>837.27</v>
+        <v>846.79</v>
       </c>
     </row>
     <row r="164">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>931.65</v>
+        <v>942.25</v>
       </c>
     </row>
     <row r="165">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>1509.26</v>
+        <v>1522.86</v>
       </c>
     </row>
     <row r="166">
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>27140.15</v>
+        <v>27196.37</v>
       </c>
     </row>
     <row r="167">
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>1678.59</v>
+        <v>1682.07</v>
       </c>
     </row>
     <row r="168">
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>1065.6</v>
+        <v>1059.21</v>
       </c>
     </row>
     <row r="169">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>1767.43</v>
+        <v>1756.83</v>
       </c>
     </row>
     <row r="170">
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>44103.36</v>
+        <v>43503.75</v>
       </c>
     </row>
     <row r="171">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>1195.53</v>
+        <v>1179.27</v>
       </c>
     </row>
     <row r="172">
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>1573.5</v>
+        <v>1560.07</v>
       </c>
     </row>
     <row r="173">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>8879.58</v>
+        <v>8946.84</v>
       </c>
     </row>
     <row r="174">
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>19657.97</v>
+        <v>19806.86</v>
       </c>
     </row>
     <row r="175">
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>1576.42</v>
+        <v>1582.39</v>
       </c>
     </row>
     <row r="176">
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>29194.01</v>
+        <v>29120.3</v>
       </c>
     </row>
     <row r="177">
@@ -11244,7 +11244,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>2661.18</v>
+        <v>2654.46</v>
       </c>
     </row>
     <row r="178">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>788.5599999999999</v>
+        <v>794.4400000000001</v>
       </c>
     </row>
     <row r="179">
@@ -11366,7 +11366,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>1609.61</v>
+        <v>1621.6</v>
       </c>
     </row>
     <row r="180">
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>901.21</v>
+        <v>892.22</v>
       </c>
     </row>
     <row r="181">
@@ -11488,7 +11488,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>850.52</v>
+        <v>842.04</v>
       </c>
     </row>
     <row r="182">
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>18490.26</v>
+        <v>18409.21</v>
       </c>
     </row>
     <row r="183">
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>1476.97</v>
+        <v>1470.49</v>
       </c>
     </row>
     <row r="184">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>7862.33</v>
+        <v>7776.8</v>
       </c>
     </row>
     <row r="185">
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>953.59</v>
+        <v>943.22</v>
       </c>
     </row>
     <row r="186">
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>788.21</v>
+        <v>792.08</v>
       </c>
     </row>
     <row r="187">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>38897.77</v>
+        <v>39026.8</v>
       </c>
     </row>
     <row r="188">
@@ -11915,7 +11915,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>1556.71</v>
+        <v>1561.67</v>
       </c>
     </row>
     <row r="189">
@@ -11976,7 +11976,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>5321.69</v>
+        <v>5338.63</v>
       </c>
     </row>
     <row r="190">
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>881.72</v>
+        <v>884.53</v>
       </c>
     </row>
     <row r="191">
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>7478.81</v>
+        <v>7518.57</v>
       </c>
     </row>
     <row r="192">
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>788.21</v>
+        <v>792.4</v>
       </c>
     </row>
     <row r="193">
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>2776.83</v>
+        <v>2816.56</v>
       </c>
     </row>
     <row r="194">
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>1051.34</v>
+        <v>1066.38</v>
       </c>
     </row>
     <row r="195">
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>1743.66</v>
+        <v>1764.12</v>
       </c>
     </row>
     <row r="196">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>2241.09</v>
+        <v>2278.99</v>
       </c>
     </row>
     <row r="197">
@@ -12464,7 +12464,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>1601.27</v>
+        <v>1628.35</v>
       </c>
     </row>
     <row r="198">
@@ -12525,7 +12525,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>962.73</v>
+        <v>955.42</v>
       </c>
     </row>
     <row r="199">
@@ -12586,7 +12586,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>4306.94</v>
+        <v>4274.27</v>
       </c>
     </row>
     <row r="200">
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>1369.96</v>
+        <v>1359.57</v>
       </c>
     </row>
     <row r="201">
@@ -12708,7 +12708,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>1200.95</v>
+        <v>1180.66</v>
       </c>
     </row>
     <row r="202">
@@ -12769,7 +12769,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>13791.67</v>
+        <v>13558.65</v>
       </c>
     </row>
     <row r="203">
@@ -12830,7 +12830,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>8823.879999999999</v>
+        <v>8698.65</v>
       </c>
     </row>
     <row r="204">
@@ -12891,7 +12891,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>6516.46</v>
+        <v>6423.98</v>
       </c>
     </row>
     <row r="205">
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>809.48</v>
+        <v>798.36</v>
       </c>
     </row>
     <row r="206">
@@ -13013,7 +13013,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>1646.45</v>
+        <v>1623.83</v>
       </c>
     </row>
     <row r="207">
@@ -13074,7 +13074,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>2007.52</v>
+        <v>1995.07</v>
       </c>
     </row>
     <row r="208">
@@ -13135,7 +13135,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>4833.06</v>
+        <v>4803.1</v>
       </c>
     </row>
     <row r="209">
@@ -13196,7 +13196,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>10221.01</v>
+        <v>10267.43</v>
       </c>
     </row>
     <row r="210">
@@ -13257,7 +13257,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>1685.79</v>
+        <v>1693.44</v>
       </c>
     </row>
     <row r="211">
@@ -13318,7 +13318,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>931.16</v>
+        <v>945.03</v>
       </c>
     </row>
     <row r="212">
@@ -13379,7 +13379,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>2361.86</v>
+        <v>2397.03</v>
       </c>
     </row>
     <row r="213">
@@ -13440,7 +13440,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>3503.5</v>
+        <v>3555.66</v>
       </c>
     </row>
     <row r="214">
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>906.6900000000001</v>
+        <v>920.1900000000001</v>
       </c>
     </row>
     <row r="215">
@@ -13562,7 +13562,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>12675.78</v>
+        <v>12916.76</v>
       </c>
     </row>
     <row r="216">
@@ -13623,7 +13623,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>3990.01</v>
+        <v>4065.86</v>
       </c>
     </row>
     <row r="217">
@@ -13684,7 +13684,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>1223.74</v>
+        <v>1251.34</v>
       </c>
     </row>
     <row r="218">
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>9508.77</v>
+        <v>9723.219999999999</v>
       </c>
     </row>
     <row r="219">
@@ -13806,7 +13806,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>794.34</v>
+        <v>812.26</v>
       </c>
     </row>
     <row r="220">
@@ -13867,7 +13867,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>7812.32</v>
+        <v>7988.51</v>
       </c>
     </row>
     <row r="221">
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>2756.74</v>
+        <v>2818.91</v>
       </c>
     </row>
     <row r="222">
@@ -13989,7 +13989,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>41804.51</v>
+        <v>42093.14</v>
       </c>
     </row>
     <row r="223">
@@ -14050,7 +14050,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>7860.31</v>
+        <v>7914.58</v>
       </c>
     </row>
     <row r="224">
@@ -14111,7 +14111,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>5545.7</v>
+        <v>5583.99</v>
       </c>
     </row>
     <row r="225">
@@ -14172,7 +14172,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>14929.01</v>
+        <v>14975.16</v>
       </c>
     </row>
     <row r="226">
@@ -14233,7 +14233,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>10990.67</v>
+        <v>10961.6</v>
       </c>
     </row>
     <row r="227">
@@ -14294,7 +14294,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>816.79</v>
+        <v>814.63</v>
       </c>
     </row>
     <row r="228">
@@ -14355,7 +14355,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>1166.84</v>
+        <v>1163.75</v>
       </c>
     </row>
     <row r="229">
@@ -14416,7 +14416,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>1316.27</v>
+        <v>1312.79</v>
       </c>
     </row>
     <row r="230">
@@ -14477,7 +14477,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>855.3</v>
+        <v>843.91</v>
       </c>
     </row>
     <row r="231">
@@ -14538,7 +14538,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>10385.35</v>
+        <v>10247.01</v>
       </c>
     </row>
     <row r="232">
@@ -14599,7 +14599,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>33776.88</v>
+        <v>33115.74</v>
       </c>
     </row>
     <row r="233">
@@ -14660,7 +14660,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>1147.01</v>
+        <v>1130.02</v>
       </c>
     </row>
     <row r="234">
@@ -14721,7 +14721,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>2528.66</v>
+        <v>2538.53</v>
       </c>
     </row>
     <row r="235">
@@ -14782,7 +14782,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>1698.39</v>
+        <v>1715.47</v>
       </c>
     </row>
     <row r="236">
@@ -14843,7 +14843,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>1483.2</v>
+        <v>1498.12</v>
       </c>
     </row>
     <row r="237">
@@ -14904,7 +14904,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>48169.35</v>
+        <v>48653.82</v>
       </c>
     </row>
     <row r="238">
@@ -14965,7 +14965,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>988.8</v>
+        <v>998.75</v>
       </c>
     </row>
     <row r="239">
@@ -15026,7 +15026,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>1133.54</v>
+        <v>1144.94</v>
       </c>
     </row>
     <row r="240">
@@ -15087,7 +15087,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>19789.47</v>
+        <v>19987.63</v>
       </c>
     </row>
     <row r="241">
@@ -15148,7 +15148,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>1574.3</v>
+        <v>1590.06</v>
       </c>
     </row>
     <row r="242">
@@ -15209,7 +15209,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>14472.31</v>
+        <v>14617.24</v>
       </c>
     </row>
     <row r="243">
@@ -15270,7 +15270,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>1876.25</v>
+        <v>1885.81</v>
       </c>
     </row>
     <row r="244">
@@ -15331,7 +15331,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>1308.51</v>
+        <v>1313.6</v>
       </c>
     </row>
     <row r="245">
@@ -15392,7 +15392,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>791.48</v>
+        <v>794.5700000000001</v>
       </c>
     </row>
     <row r="246">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>1308.51</v>
+        <v>1313.6</v>
       </c>
     </row>
     <row r="247">
@@ -15514,7 +15514,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>915.73</v>
+        <v>919.29</v>
       </c>
     </row>
     <row r="248">
@@ -15575,7 +15575,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>820.65</v>
+        <v>822.39</v>
       </c>
     </row>
     <row r="249">
@@ -15636,7 +15636,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>36229.24</v>
+        <v>36306.46</v>
       </c>
     </row>
     <row r="250">
@@ -15697,7 +15697,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>3228.35</v>
+        <v>3235.23</v>
       </c>
     </row>
     <row r="251">
@@ -15758,7 +15758,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>1914.23</v>
+        <v>1918.31</v>
       </c>
     </row>
     <row r="252">
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>1669.62</v>
+        <v>1680.8</v>
       </c>
     </row>
     <row r="253">
@@ -15880,7 +15880,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>1912.45</v>
+        <v>1925.25</v>
       </c>
     </row>
     <row r="254">
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>1236</v>
+        <v>1244.65</v>
       </c>
     </row>
     <row r="255">
@@ -16002,7 +16002,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>33080.65</v>
+        <v>33312.16</v>
       </c>
     </row>
     <row r="256">
@@ -16063,7 +16063,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>37880.29</v>
+        <v>38145.39</v>
       </c>
     </row>
     <row r="257">
@@ -16124,7 +16124,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>1167</v>
+        <v>1163.32</v>
       </c>
     </row>
     <row r="258">
@@ -16185,7 +16185,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>780.54</v>
+        <v>778.08</v>
       </c>
     </row>
     <row r="259">
@@ -16246,7 +16246,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>776.9299999999999</v>
+        <v>774.47</v>
       </c>
     </row>
     <row r="260">
@@ -16307,7 +16307,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>21430.51</v>
+        <v>21362.82</v>
       </c>
     </row>
     <row r="261">
@@ -16368,7 +16368,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>776.9299999999999</v>
+        <v>774.47</v>
       </c>
     </row>
     <row r="262">
@@ -16429,7 +16429,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>824.5700000000001</v>
+        <v>822.78</v>
       </c>
     </row>
     <row r="263">
@@ -16490,7 +16490,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>1142.29</v>
+        <v>1139.81</v>
       </c>
     </row>
     <row r="264">
@@ -16551,7 +16551,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>1731.91</v>
+        <v>1721.89</v>
       </c>
     </row>
     <row r="265">
@@ -16612,7 +16612,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>997.02</v>
+        <v>991.25</v>
       </c>
     </row>
     <row r="266">
@@ -16673,7 +16673,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>1448.06</v>
+        <v>1424.69</v>
       </c>
     </row>
     <row r="267">
@@ -16734,7 +16734,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>2524.08</v>
+        <v>2483.34</v>
       </c>
     </row>
     <row r="268">
@@ -16795,7 +16795,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>7694.78</v>
+        <v>7570.6</v>
       </c>
     </row>
     <row r="269">
@@ -16856,7 +16856,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>1468.62</v>
+        <v>1444.92</v>
       </c>
     </row>
     <row r="270">
@@ -16917,7 +16917,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>3727.34</v>
+        <v>3667.58</v>
       </c>
     </row>
     <row r="271">
@@ -16978,7 +16978,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>8946.379999999999</v>
+        <v>8896.780000000001</v>
       </c>
     </row>
     <row r="272">
@@ -17039,7 +17039,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>1562.27</v>
+        <v>1554.58</v>
       </c>
     </row>
     <row r="273">
@@ -17100,7 +17100,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>3614.21</v>
+        <v>3638.41</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/araucania.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/araucania.xlsx
@@ -928,7 +928,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +993,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1058,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1306,11 @@
           <t>76.856.309-8</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1798,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1863,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1928,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +1993,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2546,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2794,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +2981,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3046,11 @@
           <t>76.856.309-8</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3416,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4030,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4095,11 @@
           <t>76.856.309-8</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4160,11 @@
           <t>77.743.864-6</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4469,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4656,11 @@
           <t>77.601.843-0</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4721,11 @@
           <t>76.856.309-8</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +4908,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5095,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5221,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5286,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5351,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5416,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5603,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5668,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6038,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6103,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6168,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6233,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6542,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6729,11 @@
           <t>76.856.309-8</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7038,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7225,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7351,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7538,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7603,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +7729,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +7855,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +7920,11 @@
           <t>76.856.309-8</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8534,11 @@
           <t>77.601.843-0</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8599,11 @@
           <t>77.743.864-6</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +8725,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +8851,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8736,7 +8916,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +8981,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8858,7 +9046,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8980,7 +9172,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9237,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9407,7 +9607,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +9977,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +10103,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10168,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10322,7 +10538,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10444,7 +10664,11 @@
           <t>76.856.309-8</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +11034,11 @@
           <t>76.856.309-8</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10993,7 +11221,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11286,11 @@
           <t>76.856.309-8</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11237,7 +11473,11 @@
           <t>77.714.552-5</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11359,7 +11599,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11481,7 +11725,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11542,7 +11790,11 @@
           <t>77.714.552-5</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11786,7 +12038,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11847,7 +12103,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11969,7 +12229,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12152,7 +12416,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12213,7 +12481,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12518,7 +12790,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13677,7 +13953,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13738,7 +14018,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13921,7 +14205,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14104,7 +14392,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14348,7 +14640,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14531,7 +14827,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14653,7 +14953,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14775,7 +15079,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14836,7 +15144,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14897,7 +15209,11 @@
           <t>76.856.309-8</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15385,7 +15701,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15446,7 +15766,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15507,7 +15831,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15568,7 +15896,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15690,7 +16022,11 @@
           <t>76.856.309-8</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15751,7 +16087,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15934,7 +16274,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15995,7 +16339,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16056,7 +16404,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16422,7 +16774,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16605,7 +16961,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16666,7 +17026,11 @@
           <t>76.856.309-8</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16727,7 +17091,11 @@
           <t>76.856.309-8</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16849,7 +17217,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16910,7 +17282,11 @@
           <t>76.856.309-8</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16971,7 +17347,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17032,7 +17412,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17337,7 +17721,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17764,7 +18152,11 @@
           <t>76.856.309-8</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17825,7 +18217,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17886,7 +18282,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17947,7 +18347,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18191,7 +18595,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18374,7 +18782,11 @@
           <t>77.662.108-0</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18435,7 +18847,11 @@
           <t>77.103.803-4</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18618,7 +19034,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18679,7 +19099,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18740,7 +19164,11 @@
           <t>77.795.374-5</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18923,7 +19351,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19228,7 +19660,11 @@
           <t>76.856.309-8</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19472,7 +19908,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19655,7 +20095,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19716,7 +20160,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20143,7 +20591,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20204,7 +20656,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20326,7 +20782,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20814,7 +21274,11 @@
           <t>76.856.309-8</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20997,7 +21461,11 @@
           <t>77.662.108-0</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21180,7 +21648,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21241,7 +21713,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21363,7 +21839,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21424,7 +21904,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21546,7 +22030,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21790,7 +22278,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21851,7 +22343,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21973,7 +22469,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22034,7 +22534,11 @@
           <t>76.856.309-8</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22583,7 +23087,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22644,7 +23152,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr"/>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L364" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22705,7 +23217,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr"/>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L365" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22827,7 +23343,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22888,7 +23408,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr"/>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L368" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22949,7 +23473,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23010,7 +23538,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23071,7 +23603,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23132,7 +23668,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L372" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23254,7 +23794,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K374" t="inlineStr"/>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L374" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23437,7 +23981,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L377" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23925,7 +24473,11 @@
           <t>77.795.374-5</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr"/>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L385" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24047,7 +24599,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24169,7 +24725,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24596,7 +25156,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K396" t="inlineStr"/>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L396" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24657,7 +25221,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24840,7 +25408,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L400" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25023,7 +25595,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K403" t="inlineStr"/>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L403" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25389,7 +25965,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K409" t="inlineStr"/>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L409" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25511,7 +26091,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr"/>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L411" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25572,7 +26156,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K412" t="inlineStr"/>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L412" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25633,7 +26221,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25694,7 +26286,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K414" t="inlineStr"/>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L414" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25999,7 +26595,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K419" t="inlineStr"/>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L419" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26121,7 +26721,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr"/>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L421" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26487,7 +27091,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K427" t="inlineStr"/>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L427" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26548,7 +27156,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K428" t="inlineStr"/>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L428" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26609,7 +27221,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L429" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26670,7 +27286,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K430" t="inlineStr"/>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L430" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27036,7 +27656,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K436" t="inlineStr"/>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L436" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27097,7 +27721,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K437" t="inlineStr"/>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L437" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27158,7 +27786,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K438" t="inlineStr"/>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L438" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27219,7 +27851,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K439" t="inlineStr"/>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L439" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27341,7 +27977,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K441" t="inlineStr"/>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L441" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27646,7 +28286,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K446" t="inlineStr"/>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L446" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27707,7 +28351,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K447" t="inlineStr"/>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L447" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28073,7 +28721,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K453" t="inlineStr"/>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L453" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28134,7 +28786,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K454" t="inlineStr"/>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L454" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28317,7 +28973,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K457" t="inlineStr"/>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L457" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28439,7 +29099,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K459" t="inlineStr"/>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L459" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28500,7 +29164,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K460" t="inlineStr"/>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L460" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28622,7 +29290,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K462" t="inlineStr"/>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L462" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28683,7 +29355,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K463" t="inlineStr"/>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L463" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28744,7 +29420,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K464" t="inlineStr"/>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L464" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28927,7 +29607,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K467" t="inlineStr"/>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L467" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29110,7 +29794,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K470" t="inlineStr"/>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L470" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29171,7 +29859,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K471" t="inlineStr"/>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L471" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29232,7 +29924,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K472" t="inlineStr"/>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L472" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29293,7 +29989,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K473" t="inlineStr"/>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L473" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29354,7 +30054,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K474" t="inlineStr"/>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L474" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29598,7 +30302,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K478" t="inlineStr"/>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L478" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29659,7 +30367,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K479" t="inlineStr"/>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L479" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29781,7 +30493,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K481" t="inlineStr"/>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L481" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29842,7 +30558,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K482" t="inlineStr"/>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L482" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30086,7 +30806,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K486" t="inlineStr"/>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L486" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30208,7 +30932,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K488" t="inlineStr"/>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L488" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30330,7 +31058,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K490" t="inlineStr"/>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L490" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30391,7 +31123,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K491" t="inlineStr"/>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L491" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30513,7 +31249,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K493" t="inlineStr"/>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L493" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30574,7 +31314,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K494" t="inlineStr"/>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L494" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30696,7 +31440,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K496" t="inlineStr"/>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L496" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30818,7 +31566,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K498" t="inlineStr"/>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L498" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30879,7 +31631,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K499" t="inlineStr"/>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L499" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30940,7 +31696,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K500" t="inlineStr"/>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L500" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31184,7 +31944,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K504" t="inlineStr"/>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L504" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31245,7 +32009,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K505" t="inlineStr"/>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L505" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31428,7 +32196,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K508" t="inlineStr"/>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L508" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31489,7 +32261,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K509" t="inlineStr"/>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L509" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31550,7 +32326,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K510" t="inlineStr"/>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L510" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32343,7 +33123,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K523" t="inlineStr"/>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L523" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32404,7 +33188,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K524" t="inlineStr"/>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L524" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32526,7 +33314,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K526" t="inlineStr"/>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L526" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32587,7 +33379,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K527" t="inlineStr"/>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L527" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32648,7 +33444,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K528" t="inlineStr"/>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L528" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32709,7 +33509,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K529" t="inlineStr"/>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L529" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32770,7 +33574,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K530" t="inlineStr"/>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L530" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33014,7 +33822,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K534" t="inlineStr"/>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L534" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33075,7 +33887,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K535" t="inlineStr"/>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L535" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33136,7 +33952,11 @@
           <t>76.856.309-8</t>
         </is>
       </c>
-      <c r="K536" t="inlineStr"/>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L536" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33197,7 +34017,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K537" t="inlineStr"/>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L537" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33258,7 +34082,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K538" t="inlineStr"/>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L538" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33319,7 +34147,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K539" t="inlineStr"/>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L539" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33380,7 +34212,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K540" t="inlineStr"/>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L540" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33502,7 +34338,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K542" t="inlineStr"/>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L542" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33563,7 +34403,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K543" t="inlineStr"/>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L543" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33624,7 +34468,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K544" t="inlineStr"/>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L544" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33746,7 +34594,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K546" t="inlineStr"/>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L546" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34051,7 +34903,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K551" t="inlineStr"/>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L551" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34173,7 +35029,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K553" t="inlineStr"/>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L553" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34356,7 +35216,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K556" t="inlineStr"/>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L556" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34417,7 +35281,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K557" t="inlineStr"/>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L557" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34539,7 +35407,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K559" t="inlineStr"/>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L559" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34905,7 +35777,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K565" t="inlineStr"/>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L565" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34966,7 +35842,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K566" t="inlineStr"/>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L566" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35088,7 +35968,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K568" t="inlineStr"/>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L568" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35149,7 +36033,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K569" t="inlineStr"/>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L569" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35210,7 +36098,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K570" t="inlineStr"/>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L570" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35271,7 +36163,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K571" t="inlineStr"/>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L571" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35332,7 +36228,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K572" t="inlineStr"/>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L572" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35393,7 +36293,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K573" t="inlineStr"/>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L573" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35515,7 +36419,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K575" t="inlineStr"/>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L575" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35576,7 +36484,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K576" t="inlineStr"/>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L576" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35637,7 +36549,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K577" t="inlineStr"/>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L577" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35698,7 +36614,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K578" t="inlineStr"/>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L578" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36125,7 +37045,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K585" t="inlineStr"/>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L585" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36308,7 +37232,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K588" t="inlineStr"/>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L588" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36369,7 +37297,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K589" t="inlineStr"/>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L589" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36430,7 +37362,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K590" t="inlineStr"/>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L590" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36674,7 +37610,11 @@
           <t>76.856.309-8</t>
         </is>
       </c>
-      <c r="K594" t="inlineStr"/>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L594" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36735,7 +37675,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K595" t="inlineStr"/>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L595" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36796,7 +37740,11 @@
           <t>77.601.267-K</t>
         </is>
       </c>
-      <c r="K596" t="inlineStr"/>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L596" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36857,7 +37805,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K597" t="inlineStr"/>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L597" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37040,7 +37992,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K600" t="inlineStr"/>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L600" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37162,7 +38118,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K602" t="inlineStr"/>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L602" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37284,7 +38244,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K604" t="inlineStr"/>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L604" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37345,7 +38309,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K605" t="inlineStr"/>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L605" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37406,7 +38374,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K606" t="inlineStr"/>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L606" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37467,7 +38439,11 @@
           <t>77.601.801-5</t>
         </is>
       </c>
-      <c r="K607" t="inlineStr"/>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L607" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37589,7 +38565,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K609" t="inlineStr"/>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L609" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37711,7 +38691,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K611" t="inlineStr"/>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L611" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37955,7 +38939,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K615" t="inlineStr"/>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L615" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/araucania.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/araucania.xlsx
@@ -1184,7 +1184,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3481,7 +3485,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3542,7 +3550,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8351,7 +8363,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9485,7 +9501,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16152,7 +16172,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
